--- a/output/2024_grupo_etario_por_SS.xlsx
+++ b/output/2024_grupo_etario_por_SS.xlsx
@@ -306,7 +306,7 @@
     <t>Servicio de Salud Metropolitano Sur</t>
   </si>
   <si>
-    <t>Servicio de Salud Metropolitano Sur Oriente</t>
+    <t>Servicio de Salud Metropolitano Sur - Oriente</t>
   </si>
 </sst>
 </file>
